--- a/Simulacao_Salario_Cesta_Estados_2010_2024.xlsx
+++ b/Simulacao_Salario_Cesta_Estados_2010_2024.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/904989930feeffce/Documentos/GitHub/Dados-Simulados/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_340C07A2A367ADF73DFC9890E22D62B1D03C5B14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D07D8BE-B841-4166-AFDD-6B3DE88D1E19}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1060" yWindow="1060" windowWidth="17140" windowHeight="9910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="14">
   <si>
     <t>Estado</t>
   </si>
@@ -26,9 +45,6 @@
   </si>
   <si>
     <t>Custo da Cesta Básica (R$)</t>
-  </si>
-  <si>
-    <t>Relação Salário/Cesta</t>
   </si>
   <si>
     <t>SP</t>
@@ -64,8 +80,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,13 +144,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -172,7 +196,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -206,6 +230,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -240,9 +265,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -415,11 +441,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E151"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D151"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,13 +463,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
       </c>
       <c r="B2">
         <v>2010</v>
@@ -449,13 +477,10 @@
       <c r="D2">
         <v>775.36</v>
       </c>
-      <c r="E2">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>2011</v>
@@ -464,15 +489,12 @@
         <v>581.96</v>
       </c>
       <c r="D3">
-        <v>599.33</v>
-      </c>
-      <c r="E3">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>599.33000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>2012</v>
@@ -483,13 +505,10 @@
       <c r="D4">
         <v>378</v>
       </c>
-      <c r="E4">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>2013</v>
@@ -500,13 +519,10 @@
       <c r="D5">
         <v>733.09</v>
       </c>
-      <c r="E5">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>2014</v>
@@ -517,13 +533,10 @@
       <c r="D6">
         <v>654.04</v>
       </c>
-      <c r="E6">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>2015</v>
@@ -534,13 +547,10 @@
       <c r="D7">
         <v>784.95</v>
       </c>
-      <c r="E7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8">
         <v>2016</v>
@@ -551,30 +561,24 @@
       <c r="D8">
         <v>406.17</v>
       </c>
-      <c r="E8">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>2017</v>
       </c>
       <c r="C9">
-        <v>898.1799999999999</v>
+        <v>898.18</v>
       </c>
       <c r="D9">
         <v>391.7</v>
       </c>
-      <c r="E9">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10">
         <v>2018</v>
@@ -585,30 +589,24 @@
       <c r="D10">
         <v>562.38</v>
       </c>
-      <c r="E10">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11">
         <v>2019</v>
       </c>
       <c r="C11">
-        <v>1076.63</v>
+        <v>1076.6300000000001</v>
       </c>
       <c r="D11">
         <v>445.61</v>
       </c>
-      <c r="E11">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12">
         <v>2020</v>
@@ -619,30 +617,24 @@
       <c r="D12">
         <v>369.75</v>
       </c>
-      <c r="E12">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13">
         <v>2021</v>
       </c>
       <c r="C13">
-        <v>1156.41</v>
+        <v>1156.4100000000001</v>
       </c>
       <c r="D13">
         <v>483.18</v>
       </c>
-      <c r="E13">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14">
         <v>2022</v>
@@ -653,30 +645,24 @@
       <c r="D14">
         <v>692.59</v>
       </c>
-      <c r="E14">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15">
         <v>2023</v>
       </c>
       <c r="C15">
-        <v>1237.87</v>
+        <v>1237.8699999999999</v>
       </c>
       <c r="D15">
         <v>557.12</v>
       </c>
-      <c r="E15">
-        <v>2.22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16">
         <v>2024</v>
@@ -687,13 +673,10 @@
       <c r="D16">
         <v>323.23</v>
       </c>
-      <c r="E16">
-        <v>4.51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17">
         <v>2010</v>
@@ -704,47 +687,38 @@
       <c r="D17">
         <v>385.26</v>
       </c>
-      <c r="E17">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18">
         <v>2011</v>
       </c>
       <c r="C18">
-        <v>561.95</v>
+        <v>561.95000000000005</v>
       </c>
       <c r="D18">
-        <v>774.4400000000001</v>
-      </c>
-      <c r="E18">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>774.44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19">
         <v>2012</v>
       </c>
       <c r="C19">
-        <v>667.9400000000001</v>
+        <v>667.94</v>
       </c>
       <c r="D19">
         <v>704.2</v>
       </c>
-      <c r="E19">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20">
         <v>2013</v>
@@ -755,13 +729,10 @@
       <c r="D20">
         <v>348.84</v>
       </c>
-      <c r="E20">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21">
         <v>2014</v>
@@ -770,49 +741,40 @@
         <v>792.11</v>
       </c>
       <c r="D21">
-        <v>520.08</v>
-      </c>
-      <c r="E21">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>520.08000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22">
         <v>2015</v>
       </c>
       <c r="C22">
-        <v>778.3099999999999</v>
+        <v>778.31</v>
       </c>
       <c r="D22">
         <v>547.59</v>
       </c>
-      <c r="E22">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23">
         <v>2016</v>
       </c>
       <c r="C23">
-        <v>816.1900000000001</v>
+        <v>816.19</v>
       </c>
       <c r="D23">
         <v>754.66</v>
       </c>
-      <c r="E23">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24">
         <v>2017</v>
@@ -823,64 +785,52 @@
       <c r="D24">
         <v>631.26</v>
       </c>
-      <c r="E24">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25">
         <v>2018</v>
       </c>
       <c r="C25">
-        <v>984.8099999999999</v>
+        <v>984.81</v>
       </c>
       <c r="D25">
         <v>560.03</v>
       </c>
-      <c r="E25">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26">
         <v>2019</v>
       </c>
       <c r="C26">
-        <v>1107.61</v>
+        <v>1107.6099999999999</v>
       </c>
       <c r="D26">
         <v>392.43</v>
       </c>
-      <c r="E26">
-        <v>2.82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27">
         <v>2020</v>
       </c>
       <c r="C27">
-        <v>1300.88</v>
+        <v>1300.8800000000001</v>
       </c>
       <c r="D27">
-        <v>687.5700000000001</v>
-      </c>
-      <c r="E27">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>687.57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28">
         <v>2021</v>
@@ -891,13 +841,10 @@
       <c r="D28">
         <v>747.41</v>
       </c>
-      <c r="E28">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29">
         <v>2022</v>
@@ -906,15 +853,12 @@
         <v>1325.24</v>
       </c>
       <c r="D29">
-        <v>760.9400000000001</v>
-      </c>
-      <c r="E29">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>760.94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30">
         <v>2023</v>
@@ -925,13 +869,10 @@
       <c r="D30">
         <v>397.99</v>
       </c>
-      <c r="E30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31">
         <v>2024</v>
@@ -942,13 +883,10 @@
       <c r="D31">
         <v>462.67</v>
       </c>
-      <c r="E31">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B32">
         <v>2010</v>
@@ -959,13 +897,10 @@
       <c r="D32">
         <v>435.67</v>
       </c>
-      <c r="E32">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B33">
         <v>2011</v>
@@ -976,13 +911,10 @@
       <c r="D33">
         <v>478.38</v>
       </c>
-      <c r="E33">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34">
         <v>2012</v>
@@ -993,30 +925,24 @@
       <c r="D34">
         <v>571.35</v>
       </c>
-      <c r="E34">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35">
         <v>2013</v>
       </c>
       <c r="C35">
-        <v>672.6799999999999</v>
+        <v>672.68</v>
       </c>
       <c r="D35">
         <v>701.1</v>
       </c>
-      <c r="E35">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36">
         <v>2014</v>
@@ -1025,15 +951,12 @@
         <v>718.95</v>
       </c>
       <c r="D36">
-        <v>793.4400000000001</v>
-      </c>
-      <c r="E36">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>793.44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37">
         <v>2015</v>
@@ -1044,13 +967,10 @@
       <c r="D37">
         <v>399.36</v>
       </c>
-      <c r="E37">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B38">
         <v>2016</v>
@@ -1061,13 +981,10 @@
       <c r="D38">
         <v>707.73</v>
       </c>
-      <c r="E38">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39">
         <v>2017</v>
@@ -1078,30 +995,24 @@
       <c r="D39">
         <v>664.5</v>
       </c>
-      <c r="E39">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B40">
         <v>2018</v>
       </c>
       <c r="C40">
-        <v>1095.1</v>
+        <v>1095.0999999999999</v>
       </c>
       <c r="D40">
         <v>337.02</v>
       </c>
-      <c r="E40">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B41">
         <v>2019</v>
@@ -1112,13 +1023,10 @@
       <c r="D41">
         <v>357.93</v>
       </c>
-      <c r="E41">
-        <v>2.95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42">
         <v>2020</v>
@@ -1129,13 +1037,10 @@
       <c r="D42">
         <v>611.65</v>
       </c>
-      <c r="E42">
-        <v>2.07</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B43">
         <v>2021</v>
@@ -1146,13 +1051,10 @@
       <c r="D43">
         <v>331.78</v>
       </c>
-      <c r="E43">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B44">
         <v>2022</v>
@@ -1163,13 +1065,10 @@
       <c r="D44">
         <v>462.59</v>
       </c>
-      <c r="E44">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B45">
         <v>2023</v>
@@ -1180,13 +1079,10 @@
       <c r="D45">
         <v>618.78</v>
       </c>
-      <c r="E45">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B46">
         <v>2024</v>
@@ -1197,13 +1093,10 @@
       <c r="D46">
         <v>536.11</v>
       </c>
-      <c r="E46">
-        <v>2.95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B47">
         <v>2010</v>
@@ -1214,30 +1107,24 @@
       <c r="D47">
         <v>656.62</v>
       </c>
-      <c r="E47">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B48">
         <v>2011</v>
       </c>
       <c r="C48">
-        <v>582.8200000000001</v>
+        <v>582.82000000000005</v>
       </c>
       <c r="D48">
         <v>580.64</v>
       </c>
-      <c r="E48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B49">
         <v>2012</v>
@@ -1248,13 +1135,10 @@
       <c r="D49">
         <v>546.9</v>
       </c>
-      <c r="E49">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B50">
         <v>2013</v>
@@ -1265,13 +1149,10 @@
       <c r="D50">
         <v>513.77</v>
       </c>
-      <c r="E50">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B51">
         <v>2014</v>
@@ -1282,13 +1163,10 @@
       <c r="D51">
         <v>353.95</v>
       </c>
-      <c r="E51">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B52">
         <v>2015</v>
@@ -1299,13 +1177,10 @@
       <c r="D52">
         <v>618.21</v>
       </c>
-      <c r="E52">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B53">
         <v>2016</v>
@@ -1316,30 +1191,24 @@
       <c r="D53">
         <v>554.29</v>
       </c>
-      <c r="E53">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B54">
         <v>2017</v>
       </c>
       <c r="C54">
-        <v>1050.59</v>
+        <v>1050.5899999999999</v>
       </c>
       <c r="D54">
         <v>424.65</v>
       </c>
-      <c r="E54">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B55">
         <v>2018</v>
@@ -1350,13 +1219,10 @@
       <c r="D55">
         <v>677.78</v>
       </c>
-      <c r="E55">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B56">
         <v>2019</v>
@@ -1367,13 +1233,10 @@
       <c r="D56">
         <v>338.49</v>
       </c>
-      <c r="E56">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B57">
         <v>2020</v>
@@ -1384,13 +1247,10 @@
       <c r="D57">
         <v>380.61</v>
       </c>
-      <c r="E57">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B58">
         <v>2021</v>
@@ -1399,15 +1259,12 @@
         <v>1366.8</v>
       </c>
       <c r="D58">
-        <v>704.0599999999999</v>
-      </c>
-      <c r="E58">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>704.06</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B59">
         <v>2022</v>
@@ -1418,13 +1275,10 @@
       <c r="D59">
         <v>735.73</v>
       </c>
-      <c r="E59">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B60">
         <v>2023</v>
@@ -1435,13 +1289,10 @@
       <c r="D60">
         <v>393.29</v>
       </c>
-      <c r="E60">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B61">
         <v>2024</v>
@@ -1450,15 +1301,12 @@
         <v>1584.87</v>
       </c>
       <c r="D61">
-        <v>569.67</v>
-      </c>
-      <c r="E61">
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>569.66999999999996</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B62">
         <v>2010</v>
@@ -1469,13 +1317,10 @@
       <c r="D62">
         <v>748.05</v>
       </c>
-      <c r="E62">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B63">
         <v>2011</v>
@@ -1486,30 +1331,24 @@
       <c r="D63">
         <v>355.03</v>
       </c>
-      <c r="E63">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B64">
         <v>2012</v>
       </c>
       <c r="C64">
-        <v>623.6799999999999</v>
+        <v>623.67999999999995</v>
       </c>
       <c r="D64">
-        <v>513.55</v>
-      </c>
-      <c r="E64">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>513.54999999999995</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65">
         <v>2013</v>
@@ -1520,13 +1359,10 @@
       <c r="D65">
         <v>730.37</v>
       </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B66">
         <v>2014</v>
@@ -1537,13 +1373,10 @@
       <c r="D66">
         <v>555.37</v>
       </c>
-      <c r="E66">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B67">
         <v>2015</v>
@@ -1554,13 +1387,10 @@
       <c r="D67">
         <v>411.05</v>
       </c>
-      <c r="E67">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B68">
         <v>2016</v>
@@ -1571,13 +1401,10 @@
       <c r="D68">
         <v>468.81</v>
       </c>
-      <c r="E68">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B69">
         <v>2017</v>
@@ -1588,13 +1415,10 @@
       <c r="D69">
         <v>461.6</v>
       </c>
-      <c r="E69">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B70">
         <v>2018</v>
@@ -1605,13 +1429,10 @@
       <c r="D70">
         <v>651.51</v>
       </c>
-      <c r="E70">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B71">
         <v>2019</v>
@@ -1622,13 +1443,10 @@
       <c r="D71">
         <v>785.89</v>
       </c>
-      <c r="E71">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B72">
         <v>2020</v>
@@ -1639,30 +1457,24 @@
       <c r="D72">
         <v>425.89</v>
       </c>
-      <c r="E72">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B73">
         <v>2021</v>
       </c>
       <c r="C73">
-        <v>1224.09</v>
+        <v>1224.0899999999999</v>
       </c>
       <c r="D73">
         <v>450.44</v>
       </c>
-      <c r="E73">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B74">
         <v>2022</v>
@@ -1673,13 +1485,10 @@
       <c r="D74">
         <v>318.44</v>
       </c>
-      <c r="E74">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B75">
         <v>2023</v>
@@ -1690,30 +1499,24 @@
       <c r="D75">
         <v>551.34</v>
       </c>
-      <c r="E75">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B76">
         <v>2024</v>
       </c>
       <c r="C76">
-        <v>1231.62</v>
+        <v>1231.6199999999999</v>
       </c>
       <c r="D76">
         <v>439.32</v>
       </c>
-      <c r="E76">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B77">
         <v>2010</v>
@@ -1724,13 +1527,10 @@
       <c r="D77">
         <v>419.78</v>
       </c>
-      <c r="E77">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B78">
         <v>2011</v>
@@ -1741,13 +1541,10 @@
       <c r="D78">
         <v>544.73</v>
       </c>
-      <c r="E78">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B79">
         <v>2012</v>
@@ -1758,13 +1555,10 @@
       <c r="D79">
         <v>421.03</v>
       </c>
-      <c r="E79">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B80">
         <v>2013</v>
@@ -1773,15 +1567,12 @@
         <v>720.49</v>
       </c>
       <c r="D80">
-        <v>680.8099999999999</v>
-      </c>
-      <c r="E80">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>680.81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B81">
         <v>2014</v>
@@ -1792,13 +1583,10 @@
       <c r="D81">
         <v>664.11</v>
       </c>
-      <c r="E81">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B82">
         <v>2015</v>
@@ -1809,13 +1597,10 @@
       <c r="D82">
         <v>616.15</v>
       </c>
-      <c r="E82">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B83">
         <v>2016</v>
@@ -1826,13 +1611,10 @@
       <c r="D83">
         <v>567.89</v>
       </c>
-      <c r="E83">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B84">
         <v>2017</v>
@@ -1843,13 +1625,10 @@
       <c r="D84">
         <v>717.65</v>
       </c>
-      <c r="E84">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B85">
         <v>2018</v>
@@ -1860,13 +1639,10 @@
       <c r="D85">
         <v>393.26</v>
       </c>
-      <c r="E85">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B86">
         <v>2019</v>
@@ -1875,15 +1651,12 @@
         <v>971.01</v>
       </c>
       <c r="D86">
-        <v>595.45</v>
-      </c>
-      <c r="E86">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>595.45000000000005</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B87">
         <v>2020</v>
@@ -1892,15 +1665,12 @@
         <v>1213.27</v>
       </c>
       <c r="D87">
-        <v>308.29</v>
-      </c>
-      <c r="E87">
-        <v>3.94</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>308.29000000000002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B88">
         <v>2021</v>
@@ -1911,13 +1681,10 @@
       <c r="D88">
         <v>413.25</v>
       </c>
-      <c r="E88">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B89">
         <v>2022</v>
@@ -1928,13 +1695,10 @@
       <c r="D89">
         <v>387.18</v>
       </c>
-      <c r="E89">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B90">
         <v>2023</v>
@@ -1945,13 +1709,10 @@
       <c r="D90">
         <v>493.37</v>
       </c>
-      <c r="E90">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B91">
         <v>2024</v>
@@ -1962,13 +1723,10 @@
       <c r="D91">
         <v>368.76</v>
       </c>
-      <c r="E91">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B92">
         <v>2010</v>
@@ -1979,13 +1737,10 @@
       <c r="D92">
         <v>356.74</v>
       </c>
-      <c r="E92">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B93">
         <v>2011</v>
@@ -1996,13 +1751,10 @@
       <c r="D93">
         <v>738.67</v>
       </c>
-      <c r="E93">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B94">
         <v>2012</v>
@@ -2013,13 +1765,10 @@
       <c r="D94">
         <v>629.99</v>
       </c>
-      <c r="E94">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B95">
         <v>2013</v>
@@ -2030,30 +1779,24 @@
       <c r="D95">
         <v>577.6</v>
       </c>
-      <c r="E95">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B96">
         <v>2014</v>
       </c>
       <c r="C96">
-        <v>773.5599999999999</v>
+        <v>773.56</v>
       </c>
       <c r="D96">
         <v>420.93</v>
       </c>
-      <c r="E96">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B97">
         <v>2015</v>
@@ -2064,13 +1807,10 @@
       <c r="D97">
         <v>748.61</v>
       </c>
-      <c r="E97">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B98">
         <v>2016</v>
@@ -2079,15 +1819,12 @@
         <v>972.08</v>
       </c>
       <c r="D98">
-        <v>616.55</v>
-      </c>
-      <c r="E98">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>616.54999999999995</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B99">
         <v>2017</v>
@@ -2098,13 +1835,10 @@
       <c r="D99">
         <v>474.6</v>
       </c>
-      <c r="E99">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B100">
         <v>2018</v>
@@ -2113,15 +1847,12 @@
         <v>1084.23</v>
       </c>
       <c r="D100">
-        <v>748.5599999999999</v>
-      </c>
-      <c r="E100">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>748.56</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B101">
         <v>2019</v>
@@ -2130,49 +1861,40 @@
         <v>1199.51</v>
       </c>
       <c r="D101">
-        <v>689.9400000000001</v>
-      </c>
-      <c r="E101">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>689.94</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B102">
         <v>2020</v>
       </c>
       <c r="C102">
-        <v>1202.61</v>
+        <v>1202.6099999999999</v>
       </c>
       <c r="D102">
         <v>342.07</v>
       </c>
-      <c r="E102">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B103">
         <v>2021</v>
       </c>
       <c r="C103">
-        <v>1113.34</v>
+        <v>1113.3399999999999</v>
       </c>
       <c r="D103">
         <v>749.28</v>
       </c>
-      <c r="E103">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B104">
         <v>2022</v>
@@ -2181,15 +1903,12 @@
         <v>1328.31</v>
       </c>
       <c r="D104">
-        <v>304.6</v>
-      </c>
-      <c r="E104">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+        <v>304.60000000000002</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B105">
         <v>2023</v>
@@ -2200,30 +1919,24 @@
       <c r="D105">
         <v>631.75</v>
       </c>
-      <c r="E105">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B106">
         <v>2024</v>
       </c>
       <c r="C106">
-        <v>1212.13</v>
+        <v>1212.1300000000001</v>
       </c>
       <c r="D106">
         <v>380.4</v>
       </c>
-      <c r="E106">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B107">
         <v>2010</v>
@@ -2232,32 +1945,26 @@
         <v>510</v>
       </c>
       <c r="D107">
-        <v>645.95</v>
-      </c>
-      <c r="E107">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+        <v>645.95000000000005</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B108">
         <v>2011</v>
       </c>
       <c r="C108">
-        <v>579.5599999999999</v>
+        <v>579.55999999999995</v>
       </c>
       <c r="D108">
         <v>412.13</v>
       </c>
-      <c r="E108">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B109">
         <v>2012</v>
@@ -2268,13 +1975,10 @@
       <c r="D109">
         <v>418.62</v>
       </c>
-      <c r="E109">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B110">
         <v>2013</v>
@@ -2285,13 +1989,10 @@
       <c r="D110">
         <v>673.25</v>
       </c>
-      <c r="E110">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B111">
         <v>2014</v>
@@ -2302,13 +2003,10 @@
       <c r="D111">
         <v>724.61</v>
       </c>
-      <c r="E111">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B112">
         <v>2015</v>
@@ -2319,13 +2017,10 @@
       <c r="D112">
         <v>584.15</v>
       </c>
-      <c r="E112">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B113">
         <v>2016</v>
@@ -2336,30 +2031,24 @@
       <c r="D113">
         <v>483.86</v>
       </c>
-      <c r="E113">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B114">
         <v>2017</v>
       </c>
       <c r="C114">
-        <v>915.6900000000001</v>
+        <v>915.69</v>
       </c>
       <c r="D114">
         <v>421.99</v>
       </c>
-      <c r="E114">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B115">
         <v>2018</v>
@@ -2370,30 +2059,24 @@
       <c r="D115">
         <v>496.55</v>
       </c>
-      <c r="E115">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B116">
         <v>2019</v>
       </c>
       <c r="C116">
-        <v>1200.85</v>
+        <v>1200.8499999999999</v>
       </c>
       <c r="D116">
-        <v>615.5700000000001</v>
-      </c>
-      <c r="E116">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>615.57000000000005</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B117">
         <v>2020</v>
@@ -2402,32 +2085,26 @@
         <v>1248.44</v>
       </c>
       <c r="D117">
-        <v>551.3200000000001</v>
-      </c>
-      <c r="E117">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <v>551.32000000000005</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B118">
         <v>2021</v>
       </c>
       <c r="C118">
-        <v>1250.38</v>
+        <v>1250.3800000000001</v>
       </c>
       <c r="D118">
         <v>546.26</v>
       </c>
-      <c r="E118">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B119">
         <v>2022</v>
@@ -2438,13 +2115,10 @@
       <c r="D119">
         <v>661.23</v>
       </c>
-      <c r="E119">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B120">
         <v>2023</v>
@@ -2453,15 +2127,12 @@
         <v>1269.5</v>
       </c>
       <c r="D120">
-        <v>312.16</v>
-      </c>
-      <c r="E120">
-        <v>4.07</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+        <v>312.16000000000003</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B121">
         <v>2024</v>
@@ -2472,13 +2143,10 @@
       <c r="D121">
         <v>388.56</v>
       </c>
-      <c r="E121">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B122">
         <v>2010</v>
@@ -2489,47 +2157,38 @@
       <c r="D122">
         <v>776.96</v>
       </c>
-      <c r="E122">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B123">
         <v>2011</v>
       </c>
       <c r="C123">
-        <v>587.45</v>
+        <v>587.45000000000005</v>
       </c>
       <c r="D123">
         <v>485.08</v>
       </c>
-      <c r="E123">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B124">
         <v>2012</v>
       </c>
       <c r="C124">
-        <v>610.9299999999999</v>
+        <v>610.92999999999995</v>
       </c>
       <c r="D124">
         <v>764.16</v>
       </c>
-      <c r="E124">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B125">
         <v>2013</v>
@@ -2540,13 +2199,10 @@
       <c r="D125">
         <v>783.33</v>
       </c>
-      <c r="E125">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B126">
         <v>2014</v>
@@ -2557,13 +2213,10 @@
       <c r="D126">
         <v>726.5</v>
       </c>
-      <c r="E126">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B127">
         <v>2015</v>
@@ -2574,13 +2227,10 @@
       <c r="D127">
         <v>492.55</v>
       </c>
-      <c r="E127">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B128">
         <v>2016</v>
@@ -2591,13 +2241,10 @@
       <c r="D128">
         <v>458.46</v>
       </c>
-      <c r="E128">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B129">
         <v>2017</v>
@@ -2608,13 +2255,10 @@
       <c r="D129">
         <v>578.4</v>
       </c>
-      <c r="E129">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B130">
         <v>2018</v>
@@ -2625,13 +2269,10 @@
       <c r="D130">
         <v>648.01</v>
       </c>
-      <c r="E130">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B131">
         <v>2019</v>
@@ -2642,13 +2283,10 @@
       <c r="D131">
         <v>348.59</v>
       </c>
-      <c r="E131">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B132">
         <v>2020</v>
@@ -2659,13 +2297,10 @@
       <c r="D132">
         <v>795.03</v>
       </c>
-      <c r="E132">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B133">
         <v>2021</v>
@@ -2676,13 +2311,10 @@
       <c r="D133">
         <v>559.16</v>
       </c>
-      <c r="E133">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B134">
         <v>2022</v>
@@ -2693,13 +2325,10 @@
       <c r="D134">
         <v>670.38</v>
       </c>
-      <c r="E134">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B135">
         <v>2023</v>
@@ -2710,13 +2339,10 @@
       <c r="D135">
         <v>651.24</v>
       </c>
-      <c r="E135">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B136">
         <v>2024</v>
@@ -2727,13 +2353,10 @@
       <c r="D136">
         <v>446.8</v>
       </c>
-      <c r="E136">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B137">
         <v>2010</v>
@@ -2742,15 +2365,12 @@
         <v>510</v>
       </c>
       <c r="D137">
-        <v>705.0599999999999</v>
-      </c>
-      <c r="E137">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>705.06</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B138">
         <v>2011</v>
@@ -2761,30 +2381,24 @@
       <c r="D138">
         <v>756.62</v>
       </c>
-      <c r="E138">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B139">
         <v>2012</v>
       </c>
       <c r="C139">
-        <v>640.6799999999999</v>
+        <v>640.67999999999995</v>
       </c>
       <c r="D139">
         <v>550.76</v>
       </c>
-      <c r="E139">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B140">
         <v>2013</v>
@@ -2795,13 +2409,10 @@
       <c r="D140">
         <v>624.98</v>
       </c>
-      <c r="E140">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B141">
         <v>2014</v>
@@ -2812,13 +2423,10 @@
       <c r="D141">
         <v>697.9</v>
       </c>
-      <c r="E141">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B142">
         <v>2015</v>
@@ -2829,13 +2437,10 @@
       <c r="D142">
         <v>469</v>
       </c>
-      <c r="E142">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B143">
         <v>2016</v>
@@ -2846,30 +2451,24 @@
       <c r="D143">
         <v>346.99</v>
       </c>
-      <c r="E143">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B144">
         <v>2017</v>
       </c>
       <c r="C144">
-        <v>981.4400000000001</v>
+        <v>981.44</v>
       </c>
       <c r="D144">
-        <v>317.97</v>
-      </c>
-      <c r="E144">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
+        <v>317.97000000000003</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B145">
         <v>2018</v>
@@ -2878,32 +2477,26 @@
         <v>1021.74</v>
       </c>
       <c r="D145">
-        <v>571.3200000000001</v>
-      </c>
-      <c r="E145">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+        <v>571.32000000000005</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B146">
         <v>2019</v>
       </c>
       <c r="C146">
-        <v>1037.37</v>
+        <v>1037.3699999999999</v>
       </c>
       <c r="D146">
-        <v>595.42</v>
-      </c>
-      <c r="E146">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+        <v>595.41999999999996</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B147">
         <v>2020</v>
@@ -2914,13 +2507,10 @@
       <c r="D147">
         <v>318.67</v>
       </c>
-      <c r="E147">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B148">
         <v>2021</v>
@@ -2931,13 +2521,10 @@
       <c r="D148">
         <v>480.1</v>
       </c>
-      <c r="E148">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B149">
         <v>2022</v>
@@ -2948,13 +2535,10 @@
       <c r="D149">
         <v>561.12</v>
       </c>
-      <c r="E149">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B150">
         <v>2023</v>
@@ -2965,13 +2549,10 @@
       <c r="D150">
         <v>407.91</v>
       </c>
-      <c r="E150">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B151">
         <v>2024</v>
@@ -2981,9 +2562,6 @@
       </c>
       <c r="D151">
         <v>342.67</v>
-      </c>
-      <c r="E151">
-        <v>4.29</v>
       </c>
     </row>
   </sheetData>
